--- a/Slavery_dictionairy_v2.xlsx
+++ b/Slavery_dictionairy_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Home\policy-analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E3B4EB7C-6884-4130-A3A7-6A8856A65AB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF5BF179-A8D4-491E-BF95-0C647974F358}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9345" yWindow="3615" windowWidth="16200" windowHeight="11295" xr2:uid="{973A8F8D-10E1-47A5-8FD7-F2809CE333F4}"/>
+    <workbookView xWindow="1080" yWindow="1080" windowWidth="21600" windowHeight="11295" xr2:uid="{973A8F8D-10E1-47A5-8FD7-F2809CE333F4}"/>
   </bookViews>
   <sheets>
     <sheet name="Dictionary" sheetId="1" r:id="rId1"/>
@@ -1272,6 +1272,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B695B0EB-4CA9-4C50-BA45-37458D3F18BB}">
   <dimension ref="A1:F124"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="30.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
